--- a/output/2026-09-08_高交額20大_低波幅20分鐘均線篩選.xlsx
+++ b/output/2026-09-08_高交額20大_低波幅20分鐘均線篩選.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_篩選結論" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_方法論與限制" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_資料來源" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TV_連結" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="+0.00%;-0.00%"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -86,8 +87,23 @@
     <font>
       <sz val="11"/>
     </font>
+    <font>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -129,6 +145,11 @@
         <fgColor rgb="00FDECEC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F5FB"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -156,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -221,6 +242,61 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -300,7 +376,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="11"/>
   <chart>
     <title>
       <tx>
@@ -737,6 +812,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -788,7 +864,7 @@
       <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
@@ -827,7 +903,7 @@
       <c r="A6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>TSLA</t>
         </is>
@@ -866,12 +942,12 @@
       <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
@@ -903,7 +979,7 @@
       <c r="A8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>INTC</t>
         </is>
@@ -942,7 +1018,7 @@
       <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>AVGO</t>
         </is>
@@ -979,7 +1055,7 @@
       <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>AAPL</t>
         </is>
@@ -1016,7 +1092,7 @@
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
@@ -1053,7 +1129,7 @@
       <c r="A12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>MU</t>
         </is>
@@ -1090,7 +1166,7 @@
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>ORCL</t>
         </is>
@@ -1127,7 +1203,7 @@
       <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="32" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
@@ -1164,7 +1240,7 @@
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>QCOM</t>
         </is>
@@ -1201,7 +1277,7 @@
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="32" t="inlineStr">
         <is>
           <t>META</t>
         </is>
@@ -1236,7 +1312,7 @@
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
@@ -1273,7 +1349,7 @@
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="32" t="inlineStr">
         <is>
           <t>PLTR</t>
         </is>
@@ -1310,7 +1386,7 @@
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>NFLX</t>
         </is>
@@ -1345,7 +1421,7 @@
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="32" t="inlineStr">
         <is>
           <t>CRWV</t>
         </is>
@@ -1380,12 +1456,12 @@
       <c r="A21" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>IREN</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="32" t="inlineStr">
         <is>
           <t>IREN</t>
         </is>
@@ -1417,7 +1493,7 @@
       <c r="A22" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="32" t="inlineStr">
         <is>
           <t>SOFI</t>
         </is>
@@ -1454,7 +1530,7 @@
       <c r="A23" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="32" t="inlineStr">
         <is>
           <t>PFE</t>
         </is>
@@ -1489,7 +1565,7 @@
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="32" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
@@ -1527,8 +1603,32 @@
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId23"/>
 </worksheet>
 </file>
 
@@ -1563,6 +1663,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1599,7 +1700,7 @@
       <c r="A5" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
@@ -1626,7 +1727,7 @@
       <c r="A6" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>AVGO</t>
         </is>
@@ -1653,7 +1754,7 @@
       <c r="A7" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>AAPL</t>
         </is>
@@ -1678,7 +1779,7 @@
       <c r="A8" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
@@ -1702,7 +1803,7 @@
       <c r="A9" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>ORCL</t>
         </is>
@@ -1724,6 +1825,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
@@ -1756,7 +1858,7 @@
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>TSLA</t>
         </is>
@@ -1776,7 +1878,7 @@
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
@@ -1796,7 +1898,7 @@
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
@@ -1816,7 +1918,7 @@
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>INTC</t>
         </is>
@@ -1836,7 +1938,7 @@
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>QCOM</t>
         </is>
@@ -1856,7 +1958,7 @@
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>IREN</t>
         </is>
@@ -1874,7 +1976,7 @@
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>CRWV</t>
         </is>
@@ -1892,7 +1994,7 @@
       </c>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>MU</t>
         </is>
@@ -1910,7 +2012,7 @@
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="27" t="inlineStr">
         <is>
           <t>PLTR</t>
         </is>
@@ -1928,7 +2030,7 @@
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>SOFI</t>
         </is>
@@ -1947,6 +2049,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="22" t="inlineStr">
         <is>
@@ -1972,6 +2075,23 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1996,6 +2116,8 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4" ht="71" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
         <is>
@@ -2102,6 +2224,8 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2199,7 +2323,7 @@
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>SOFI 日內高低</t>
         </is>
@@ -2211,7 +2335,7 @@
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>BE (Bloom Energy)</t>
         </is>
@@ -2223,7 +2347,7 @@
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>IREN</t>
         </is>
@@ -2262,6 +2386,556 @@
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId3"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TradingView 連結索引（本檔案出現過的所有代號）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>原地已加連結的儲存格：0 個。另有 5 個儲存格同時提及多個代號 —— Excel 不支援在單一儲存格內為部分文字加連結，故該類儲存格不在原地處理，改由本表覆蓋。點擊下方連結即可開啟該代號的 TradingView 圖表。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="C4" s="29" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="D4" s="29" t="inlineStr">
+        <is>
+          <t>出現位置</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="38" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="C5" s="40" t="inlineStr">
+        <is>
+          <t>NASDAQ:AAPL</t>
+        </is>
+      </c>
+      <c r="D5" s="33" t="inlineStr">
+        <is>
+          <t>01_高交額20大!B10、02_篩選結論!B7、02_篩選結論!F7、02_篩選結論!F8、02_篩選結論!A25、04_資料來源!A11</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="41" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B6" s="42" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C6" s="43" t="inlineStr">
+        <is>
+          <t>NASDAQ:AMD</t>
+        </is>
+      </c>
+      <c r="D6" s="37" t="inlineStr">
+        <is>
+          <t>01_高交額20大!B7、01_高交額20大!C7、02_篩選結論!A15、04_資料來源!A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="38" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B7" s="39" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C7" s="40" t="inlineStr">
+        <is>
+          <t>NASDAQ:AMZN</t>
+        </is>
+      </c>
+      <c r="D7" s="33" t="inlineStr">
+        <is>
+          <t>01_高交額20大!B14、04_資料來源!A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="41" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B8" s="42" t="inlineStr">
+        <is>
+          <t>Broadcom</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="inlineStr">
+        <is>
+          <t>NASDAQ:AVGO</t>
+        </is>
+      </c>
+      <c r="D8" s="37" t="inlineStr">
+        <is>
+          <t>01_高交額20大!B9、02_篩選結論!B6、02_篩選結論!A25、04_資料來源!A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="38" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B9" s="39" t="inlineStr">
+        <is>
+          <t>Bloom Energy</t>
+        </is>
+      </c>
+      <c r="C9" s="40" t="inlineStr">
+        <is>
+          <t>NYSE:BE</t>
+        </is>
+      </c>
+      <c r="D9" s="33" t="inlineStr">
+        <is>
+          <t>01_高交額20大!B24、02_篩選結論!A14、04_資料來源!A13</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="41" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="B10" s="42" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="inlineStr">
+        <is>
+          <t>NASDAQ:CRWV</t>
+        </is>
+      </c>
+      <c r="D10" s="37" t="inlineStr">
+        <is>
+          <t>01_高交額20大!B20、02_篩選結論!A19</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="38" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>Alphabet</t>
+        </is>
+      </c>
+      <c r="C11" s="40" t="inlineStr">
+        <is>
+          <t>NASDAQ:GOOGL</t>
+        </is>
+      </c>
+      <c r="D11" s="33" t="inlineStr">
+        <is>
+          <t>01_高交額20大!B17、04_資料來源!A11</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="41" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B12" s="42" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="C12" s="43" t="inlineStr">
+        <is>
+          <t>NASDAQ:INTC</t>
+        </is>
+      </c>
+      <c r="D12" s="37" t="inlineStr">
+        <is>
+          <t>01_高交額20大!B8、02_篩選結論!A16、04_資料來源!A10、04_資料來源!A11</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="38" t="inlineStr">
+        <is>
+          <t>IREN</t>
+        </is>
+      </c>
+      <c r="B13" s="39" t="inlineStr">
+        <is>
+          <t>IREN</t>
+        </is>
+      </c>
+      <c r="C13" s="40" t="inlineStr">
+        <is>
+          <t>NASDAQ:IREN</t>
+        </is>
+      </c>
+      <c r="D13" s="33" t="inlineStr">
+        <is>
+          <t>01_高交額20大!B21、01_高交額20大!C21、02_篩選結論!A18、04_資料來源!A14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="41" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B14" s="42" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="C14" s="43" t="inlineStr">
+        <is>
+          <t>NASDAQ:META</t>
+        </is>
+      </c>
+      <c r="D14" s="37" t="inlineStr">
+        <is>
+          <t>01_高交額20大!B16</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="38" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B15" s="39" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="C15" s="40" t="inlineStr">
+        <is>
+          <t>NASDAQ:MSFT</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="inlineStr">
+        <is>
+          <t>01_高交額20大!B11、02_篩選結論!B8、02_篩選結論!A25、04_資料來源!A11</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="41" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B16" s="42" t="inlineStr">
+        <is>
+          <t>Micron</t>
+        </is>
+      </c>
+      <c r="C16" s="43" t="inlineStr">
+        <is>
+          <t>NASDAQ:MU</t>
+        </is>
+      </c>
+      <c r="D16" s="37" t="inlineStr">
+        <is>
+          <t>01_高交額20大!B12、02_篩選結論!A20、04_資料來源!A11</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="38" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B17" s="39" t="inlineStr">
+        <is>
+          <t>Netflix</t>
+        </is>
+      </c>
+      <c r="C17" s="40" t="inlineStr">
+        <is>
+          <t>NASDAQ:NFLX</t>
+        </is>
+      </c>
+      <c r="D17" s="33" t="inlineStr">
+        <is>
+          <t>01_高交額20大!B19</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="41" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B18" s="42" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C18" s="43" t="inlineStr">
+        <is>
+          <t>NASDAQ:NVDA</t>
+        </is>
+      </c>
+      <c r="D18" s="37" t="inlineStr">
+        <is>
+          <t>01_高交額20大!B5、02_篩選結論!B5、02_篩選結論!A25、04_資料來源!A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="38" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C19" s="40" t="inlineStr">
+        <is>
+          <t>NYSE:ORCL</t>
+        </is>
+      </c>
+      <c r="D19" s="33" t="inlineStr">
+        <is>
+          <t>01_高交額20大!B13、02_篩選結論!B9、04_資料來源!A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="41" t="inlineStr">
+        <is>
+          <t>PFE</t>
+        </is>
+      </c>
+      <c r="B20" s="42" t="inlineStr">
+        <is>
+          <t>Pfizer</t>
+        </is>
+      </c>
+      <c r="C20" s="43" t="inlineStr">
+        <is>
+          <t>NYSE:PFE</t>
+        </is>
+      </c>
+      <c r="D20" s="37" t="inlineStr">
+        <is>
+          <t>01_高交額20大!B23</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="38" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B21" s="39" t="inlineStr">
+        <is>
+          <t>Palantir</t>
+        </is>
+      </c>
+      <c r="C21" s="40" t="inlineStr">
+        <is>
+          <t>NASDAQ:PLTR</t>
+        </is>
+      </c>
+      <c r="D21" s="33" t="inlineStr">
+        <is>
+          <t>01_高交額20大!B18、02_篩選結論!A21、04_資料來源!A11</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="41" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="B22" s="42" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C22" s="43" t="inlineStr">
+        <is>
+          <t>NASDAQ:QCOM</t>
+        </is>
+      </c>
+      <c r="D22" s="37" t="inlineStr">
+        <is>
+          <t>01_高交額20大!B15、02_篩選結論!A17、03_方法論與限制!B7、04_資料來源!A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="38" t="inlineStr">
+        <is>
+          <t>SOFI</t>
+        </is>
+      </c>
+      <c r="B23" s="39" t="inlineStr">
+        <is>
+          <t>SoFi Technologies</t>
+        </is>
+      </c>
+      <c r="C23" s="40" t="inlineStr">
+        <is>
+          <t>NASDAQ:SOFI</t>
+        </is>
+      </c>
+      <c r="D23" s="33" t="inlineStr">
+        <is>
+          <t>01_高交額20大!B22、02_篩選結論!A22、04_資料來源!A12</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="41" t="inlineStr">
+        <is>
+          <t>SOXX</t>
+        </is>
+      </c>
+      <c r="B24" s="42" t="inlineStr">
+        <is>
+          <t>iShares 半導體 ETF</t>
+        </is>
+      </c>
+      <c r="C24" s="43" t="inlineStr">
+        <is>
+          <t>NASDAQ:SOXX</t>
+        </is>
+      </c>
+      <c r="D24" s="37" t="inlineStr">
+        <is>
+          <t>01_高交額20大!I5、02_篩選結論!F6、04_資料來源!A10</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="38" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B25" s="39" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C25" s="40" t="inlineStr">
+        <is>
+          <t>NASDAQ:TSLA</t>
+        </is>
+      </c>
+      <c r="D25" s="33" t="inlineStr">
+        <is>
+          <t>01_高交額20大!B6、02_篩選結論!A13、04_資料來源!A8</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/2026-09-08_高交額20大_低波幅20分鐘均線篩選.xlsx
+++ b/output/2026-09-08_高交額20大_低波幅20分鐘均線篩選.xlsx
@@ -177,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -279,6 +279,24 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -864,7 +882,7 @@
       <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="32" t="inlineStr">
+      <c r="B5" s="40" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
@@ -903,7 +921,7 @@
       <c r="A6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>TSLA</t>
         </is>
@@ -942,12 +960,12 @@
       <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="32" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="C7" s="32" t="inlineStr">
+      <c r="C7" s="40" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
@@ -979,7 +997,7 @@
       <c r="A8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="32" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>INTC</t>
         </is>
@@ -1018,7 +1036,7 @@
       <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>AVGO</t>
         </is>
@@ -1055,7 +1073,7 @@
       <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="32" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>AAPL</t>
         </is>
@@ -1092,7 +1110,7 @@
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="32" t="inlineStr">
+      <c r="B11" s="40" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
@@ -1129,7 +1147,7 @@
       <c r="A12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="32" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>MU</t>
         </is>
@@ -1166,7 +1184,7 @@
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="32" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>ORCL</t>
         </is>
@@ -1203,7 +1221,7 @@
       <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="32" t="inlineStr">
+      <c r="B14" s="40" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
@@ -1240,7 +1258,7 @@
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="32" t="inlineStr">
+      <c r="B15" s="40" t="inlineStr">
         <is>
           <t>QCOM</t>
         </is>
@@ -1277,7 +1295,7 @@
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="32" t="inlineStr">
+      <c r="B16" s="40" t="inlineStr">
         <is>
           <t>META</t>
         </is>
@@ -1312,7 +1330,7 @@
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
@@ -1349,7 +1367,7 @@
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="32" t="inlineStr">
+      <c r="B18" s="40" t="inlineStr">
         <is>
           <t>PLTR</t>
         </is>
@@ -1386,7 +1404,7 @@
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="32" t="inlineStr">
+      <c r="B19" s="40" t="inlineStr">
         <is>
           <t>NFLX</t>
         </is>
@@ -1421,7 +1439,7 @@
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="32" t="inlineStr">
+      <c r="B20" s="40" t="inlineStr">
         <is>
           <t>CRWV</t>
         </is>
@@ -1456,12 +1474,12 @@
       <c r="A21" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="32" t="inlineStr">
+      <c r="B21" s="40" t="inlineStr">
         <is>
           <t>IREN</t>
         </is>
       </c>
-      <c r="C21" s="32" t="inlineStr">
+      <c r="C21" s="40" t="inlineStr">
         <is>
           <t>IREN</t>
         </is>
@@ -1493,7 +1511,7 @@
       <c r="A22" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="32" t="inlineStr">
+      <c r="B22" s="40" t="inlineStr">
         <is>
           <t>SOFI</t>
         </is>
@@ -1530,7 +1548,7 @@
       <c r="A23" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="32" t="inlineStr">
+      <c r="B23" s="40" t="inlineStr">
         <is>
           <t>PFE</t>
         </is>
@@ -1565,7 +1583,7 @@
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="32" t="inlineStr">
+      <c r="B24" s="40" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
@@ -2447,17 +2465,17 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="38" t="inlineStr">
+      <c r="A5" s="44" t="inlineStr">
         <is>
           <t>AAPL</t>
         </is>
       </c>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="45" t="inlineStr">
         <is>
           <t>Apple</t>
         </is>
       </c>
-      <c r="C5" s="40" t="inlineStr">
+      <c r="C5" s="46" t="inlineStr">
         <is>
           <t>NASDAQ:AAPL</t>
         </is>
@@ -2469,17 +2487,17 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="41" t="inlineStr">
+      <c r="A6" s="47" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B6" s="48" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="C6" s="43" t="inlineStr">
+      <c r="C6" s="49" t="inlineStr">
         <is>
           <t>NASDAQ:AMD</t>
         </is>
@@ -2491,17 +2509,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="38" t="inlineStr">
+      <c r="A7" s="44" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="B7" s="39" t="inlineStr">
+      <c r="B7" s="45" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="C7" s="40" t="inlineStr">
+      <c r="C7" s="46" t="inlineStr">
         <is>
           <t>NASDAQ:AMZN</t>
         </is>
@@ -2513,17 +2531,17 @@
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="41" t="inlineStr">
+      <c r="A8" s="47" t="inlineStr">
         <is>
           <t>AVGO</t>
         </is>
       </c>
-      <c r="B8" s="42" t="inlineStr">
+      <c r="B8" s="48" t="inlineStr">
         <is>
           <t>Broadcom</t>
         </is>
       </c>
-      <c r="C8" s="43" t="inlineStr">
+      <c r="C8" s="49" t="inlineStr">
         <is>
           <t>NASDAQ:AVGO</t>
         </is>
@@ -2535,17 +2553,17 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="38" t="inlineStr">
+      <c r="A9" s="44" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="B9" s="39" t="inlineStr">
+      <c r="B9" s="45" t="inlineStr">
         <is>
           <t>Bloom Energy</t>
         </is>
       </c>
-      <c r="C9" s="40" t="inlineStr">
+      <c r="C9" s="46" t="inlineStr">
         <is>
           <t>NYSE:BE</t>
         </is>
@@ -2557,17 +2575,17 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="41" t="inlineStr">
+      <c r="A10" s="47" t="inlineStr">
         <is>
           <t>CRWV</t>
         </is>
       </c>
-      <c r="B10" s="42" t="inlineStr">
+      <c r="B10" s="48" t="inlineStr">
         <is>
           <t>CoreWeave</t>
         </is>
       </c>
-      <c r="C10" s="43" t="inlineStr">
+      <c r="C10" s="49" t="inlineStr">
         <is>
           <t>NASDAQ:CRWV</t>
         </is>
@@ -2579,17 +2597,17 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="44" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B11" s="39" t="inlineStr">
+      <c r="B11" s="45" t="inlineStr">
         <is>
           <t>Alphabet</t>
         </is>
       </c>
-      <c r="C11" s="40" t="inlineStr">
+      <c r="C11" s="46" t="inlineStr">
         <is>
           <t>NASDAQ:GOOGL</t>
         </is>
@@ -2601,17 +2619,17 @@
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="41" t="inlineStr">
+      <c r="A12" s="47" t="inlineStr">
         <is>
           <t>INTC</t>
         </is>
       </c>
-      <c r="B12" s="42" t="inlineStr">
+      <c r="B12" s="48" t="inlineStr">
         <is>
           <t>Intel</t>
         </is>
       </c>
-      <c r="C12" s="43" t="inlineStr">
+      <c r="C12" s="49" t="inlineStr">
         <is>
           <t>NASDAQ:INTC</t>
         </is>
@@ -2623,17 +2641,17 @@
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="38" t="inlineStr">
+      <c r="A13" s="44" t="inlineStr">
         <is>
           <t>IREN</t>
         </is>
       </c>
-      <c r="B13" s="39" t="inlineStr">
+      <c r="B13" s="45" t="inlineStr">
         <is>
           <t>IREN</t>
         </is>
       </c>
-      <c r="C13" s="40" t="inlineStr">
+      <c r="C13" s="46" t="inlineStr">
         <is>
           <t>NASDAQ:IREN</t>
         </is>
@@ -2645,17 +2663,17 @@
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="41" t="inlineStr">
+      <c r="A14" s="47" t="inlineStr">
         <is>
           <t>META</t>
         </is>
       </c>
-      <c r="B14" s="42" t="inlineStr">
+      <c r="B14" s="48" t="inlineStr">
         <is>
           <t>Meta Platforms</t>
         </is>
       </c>
-      <c r="C14" s="43" t="inlineStr">
+      <c r="C14" s="49" t="inlineStr">
         <is>
           <t>NASDAQ:META</t>
         </is>
@@ -2667,17 +2685,17 @@
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="38" t="inlineStr">
+      <c r="A15" s="44" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B15" s="39" t="inlineStr">
+      <c r="B15" s="45" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="C15" s="40" t="inlineStr">
+      <c r="C15" s="46" t="inlineStr">
         <is>
           <t>NASDAQ:MSFT</t>
         </is>
@@ -2689,17 +2707,17 @@
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="41" t="inlineStr">
+      <c r="A16" s="47" t="inlineStr">
         <is>
           <t>MU</t>
         </is>
       </c>
-      <c r="B16" s="42" t="inlineStr">
+      <c r="B16" s="48" t="inlineStr">
         <is>
           <t>Micron</t>
         </is>
       </c>
-      <c r="C16" s="43" t="inlineStr">
+      <c r="C16" s="49" t="inlineStr">
         <is>
           <t>NASDAQ:MU</t>
         </is>
@@ -2711,17 +2729,17 @@
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="38" t="inlineStr">
+      <c r="A17" s="44" t="inlineStr">
         <is>
           <t>NFLX</t>
         </is>
       </c>
-      <c r="B17" s="39" t="inlineStr">
+      <c r="B17" s="45" t="inlineStr">
         <is>
           <t>Netflix</t>
         </is>
       </c>
-      <c r="C17" s="40" t="inlineStr">
+      <c r="C17" s="46" t="inlineStr">
         <is>
           <t>NASDAQ:NFLX</t>
         </is>
@@ -2733,17 +2751,17 @@
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="41" t="inlineStr">
+      <c r="A18" s="47" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B18" s="42" t="inlineStr">
+      <c r="B18" s="48" t="inlineStr">
         <is>
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="C18" s="43" t="inlineStr">
+      <c r="C18" s="49" t="inlineStr">
         <is>
           <t>NASDAQ:NVDA</t>
         </is>
@@ -2755,17 +2773,17 @@
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="38" t="inlineStr">
+      <c r="A19" s="44" t="inlineStr">
         <is>
           <t>ORCL</t>
         </is>
       </c>
-      <c r="B19" s="39" t="inlineStr">
+      <c r="B19" s="45" t="inlineStr">
         <is>
           <t>Oracle</t>
         </is>
       </c>
-      <c r="C19" s="40" t="inlineStr">
+      <c r="C19" s="46" t="inlineStr">
         <is>
           <t>NYSE:ORCL</t>
         </is>
@@ -2777,17 +2795,17 @@
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="41" t="inlineStr">
+      <c r="A20" s="47" t="inlineStr">
         <is>
           <t>PFE</t>
         </is>
       </c>
-      <c r="B20" s="42" t="inlineStr">
+      <c r="B20" s="48" t="inlineStr">
         <is>
           <t>Pfizer</t>
         </is>
       </c>
-      <c r="C20" s="43" t="inlineStr">
+      <c r="C20" s="49" t="inlineStr">
         <is>
           <t>NYSE:PFE</t>
         </is>
@@ -2799,17 +2817,17 @@
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="38" t="inlineStr">
+      <c r="A21" s="44" t="inlineStr">
         <is>
           <t>PLTR</t>
         </is>
       </c>
-      <c r="B21" s="39" t="inlineStr">
+      <c r="B21" s="45" t="inlineStr">
         <is>
           <t>Palantir</t>
         </is>
       </c>
-      <c r="C21" s="40" t="inlineStr">
+      <c r="C21" s="46" t="inlineStr">
         <is>
           <t>NASDAQ:PLTR</t>
         </is>
@@ -2821,17 +2839,17 @@
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="41" t="inlineStr">
+      <c r="A22" s="47" t="inlineStr">
         <is>
           <t>QCOM</t>
         </is>
       </c>
-      <c r="B22" s="42" t="inlineStr">
+      <c r="B22" s="48" t="inlineStr">
         <is>
           <t>Qualcomm</t>
         </is>
       </c>
-      <c r="C22" s="43" t="inlineStr">
+      <c r="C22" s="49" t="inlineStr">
         <is>
           <t>NASDAQ:QCOM</t>
         </is>
@@ -2843,17 +2861,17 @@
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="38" t="inlineStr">
+      <c r="A23" s="44" t="inlineStr">
         <is>
           <t>SOFI</t>
         </is>
       </c>
-      <c r="B23" s="39" t="inlineStr">
+      <c r="B23" s="45" t="inlineStr">
         <is>
           <t>SoFi Technologies</t>
         </is>
       </c>
-      <c r="C23" s="40" t="inlineStr">
+      <c r="C23" s="46" t="inlineStr">
         <is>
           <t>NASDAQ:SOFI</t>
         </is>
@@ -2865,17 +2883,17 @@
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="41" t="inlineStr">
+      <c r="A24" s="47" t="inlineStr">
         <is>
           <t>SOXX</t>
         </is>
       </c>
-      <c r="B24" s="42" t="inlineStr">
+      <c r="B24" s="48" t="inlineStr">
         <is>
           <t>iShares 半導體 ETF</t>
         </is>
       </c>
-      <c r="C24" s="43" t="inlineStr">
+      <c r="C24" s="49" t="inlineStr">
         <is>
           <t>NASDAQ:SOXX</t>
         </is>
@@ -2887,17 +2905,17 @@
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="38" t="inlineStr">
+      <c r="A25" s="44" t="inlineStr">
         <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B25" s="39" t="inlineStr">
+      <c r="B25" s="45" t="inlineStr">
         <is>
           <t>Tesla</t>
         </is>
       </c>
-      <c r="C25" s="40" t="inlineStr">
+      <c r="C25" s="46" t="inlineStr">
         <is>
           <t>NASDAQ:TSLA</t>
         </is>

--- a/output/2026-09-08_高交額20大_低波幅20分鐘均線篩選.xlsx
+++ b/output/2026-09-08_高交額20大_低波幅20分鐘均線篩選.xlsx
@@ -177,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -279,6 +279,60 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -882,7 +936,7 @@
       <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="40" t="inlineStr">
+      <c r="B5" s="58" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
@@ -921,7 +975,7 @@
       <c r="A6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="40" t="inlineStr">
+      <c r="B6" s="58" t="inlineStr">
         <is>
           <t>TSLA</t>
         </is>
@@ -960,12 +1014,12 @@
       <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B7" s="58" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="C7" s="40" t="inlineStr">
+      <c r="C7" s="58" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
@@ -997,7 +1051,7 @@
       <c r="A8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="40" t="inlineStr">
+      <c r="B8" s="58" t="inlineStr">
         <is>
           <t>INTC</t>
         </is>
@@ -1036,7 +1090,7 @@
       <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="40" t="inlineStr">
+      <c r="B9" s="58" t="inlineStr">
         <is>
           <t>AVGO</t>
         </is>
@@ -1073,7 +1127,7 @@
       <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="40" t="inlineStr">
+      <c r="B10" s="58" t="inlineStr">
         <is>
           <t>AAPL</t>
         </is>
@@ -1110,7 +1164,7 @@
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="40" t="inlineStr">
+      <c r="B11" s="58" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
@@ -1147,7 +1201,7 @@
       <c r="A12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="40" t="inlineStr">
+      <c r="B12" s="58" t="inlineStr">
         <is>
           <t>MU</t>
         </is>
@@ -1184,7 +1238,7 @@
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="40" t="inlineStr">
+      <c r="B13" s="58" t="inlineStr">
         <is>
           <t>ORCL</t>
         </is>
@@ -1221,7 +1275,7 @@
       <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="40" t="inlineStr">
+      <c r="B14" s="58" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
@@ -1258,7 +1312,7 @@
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="40" t="inlineStr">
+      <c r="B15" s="58" t="inlineStr">
         <is>
           <t>QCOM</t>
         </is>
@@ -1295,7 +1349,7 @@
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="40" t="inlineStr">
+      <c r="B16" s="58" t="inlineStr">
         <is>
           <t>META</t>
         </is>
@@ -1330,7 +1384,7 @@
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="40" t="inlineStr">
+      <c r="B17" s="58" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
@@ -1367,7 +1421,7 @@
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="40" t="inlineStr">
+      <c r="B18" s="58" t="inlineStr">
         <is>
           <t>PLTR</t>
         </is>
@@ -1404,7 +1458,7 @@
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="40" t="inlineStr">
+      <c r="B19" s="58" t="inlineStr">
         <is>
           <t>NFLX</t>
         </is>
@@ -1439,7 +1493,7 @@
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="40" t="inlineStr">
+      <c r="B20" s="58" t="inlineStr">
         <is>
           <t>CRWV</t>
         </is>
@@ -1474,12 +1528,12 @@
       <c r="A21" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="40" t="inlineStr">
+      <c r="B21" s="58" t="inlineStr">
         <is>
           <t>IREN</t>
         </is>
       </c>
-      <c r="C21" s="40" t="inlineStr">
+      <c r="C21" s="58" t="inlineStr">
         <is>
           <t>IREN</t>
         </is>
@@ -1511,7 +1565,7 @@
       <c r="A22" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="40" t="inlineStr">
+      <c r="B22" s="58" t="inlineStr">
         <is>
           <t>SOFI</t>
         </is>
@@ -1548,7 +1602,7 @@
       <c r="A23" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="40" t="inlineStr">
+      <c r="B23" s="58" t="inlineStr">
         <is>
           <t>PFE</t>
         </is>
@@ -1583,7 +1637,7 @@
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="40" t="inlineStr">
+      <c r="B24" s="58" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
@@ -2465,17 +2519,17 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="44" t="inlineStr">
+      <c r="A5" s="62" t="inlineStr">
         <is>
           <t>AAPL</t>
         </is>
       </c>
-      <c r="B5" s="45" t="inlineStr">
+      <c r="B5" s="63" t="inlineStr">
         <is>
           <t>Apple</t>
         </is>
       </c>
-      <c r="C5" s="46" t="inlineStr">
+      <c r="C5" s="64" t="inlineStr">
         <is>
           <t>NASDAQ:AAPL</t>
         </is>
@@ -2487,17 +2541,17 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="47" t="inlineStr">
+      <c r="A6" s="65" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="B6" s="48" t="inlineStr">
+      <c r="B6" s="66" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="C6" s="49" t="inlineStr">
+      <c r="C6" s="67" t="inlineStr">
         <is>
           <t>NASDAQ:AMD</t>
         </is>
@@ -2509,17 +2563,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="44" t="inlineStr">
+      <c r="A7" s="62" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="B7" s="45" t="inlineStr">
+      <c r="B7" s="63" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="C7" s="46" t="inlineStr">
+      <c r="C7" s="64" t="inlineStr">
         <is>
           <t>NASDAQ:AMZN</t>
         </is>
@@ -2531,17 +2585,17 @@
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="47" t="inlineStr">
+      <c r="A8" s="65" t="inlineStr">
         <is>
           <t>AVGO</t>
         </is>
       </c>
-      <c r="B8" s="48" t="inlineStr">
+      <c r="B8" s="66" t="inlineStr">
         <is>
           <t>Broadcom</t>
         </is>
       </c>
-      <c r="C8" s="49" t="inlineStr">
+      <c r="C8" s="67" t="inlineStr">
         <is>
           <t>NASDAQ:AVGO</t>
         </is>
@@ -2553,17 +2607,17 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="44" t="inlineStr">
+      <c r="A9" s="62" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="B9" s="45" t="inlineStr">
+      <c r="B9" s="63" t="inlineStr">
         <is>
           <t>Bloom Energy</t>
         </is>
       </c>
-      <c r="C9" s="46" t="inlineStr">
+      <c r="C9" s="64" t="inlineStr">
         <is>
           <t>NYSE:BE</t>
         </is>
@@ -2575,17 +2629,17 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="47" t="inlineStr">
+      <c r="A10" s="65" t="inlineStr">
         <is>
           <t>CRWV</t>
         </is>
       </c>
-      <c r="B10" s="48" t="inlineStr">
+      <c r="B10" s="66" t="inlineStr">
         <is>
           <t>CoreWeave</t>
         </is>
       </c>
-      <c r="C10" s="49" t="inlineStr">
+      <c r="C10" s="67" t="inlineStr">
         <is>
           <t>NASDAQ:CRWV</t>
         </is>
@@ -2597,17 +2651,17 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="44" t="inlineStr">
+      <c r="A11" s="62" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B11" s="45" t="inlineStr">
+      <c r="B11" s="63" t="inlineStr">
         <is>
           <t>Alphabet</t>
         </is>
       </c>
-      <c r="C11" s="46" t="inlineStr">
+      <c r="C11" s="64" t="inlineStr">
         <is>
           <t>NASDAQ:GOOGL</t>
         </is>
@@ -2619,17 +2673,17 @@
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="47" t="inlineStr">
+      <c r="A12" s="65" t="inlineStr">
         <is>
           <t>INTC</t>
         </is>
       </c>
-      <c r="B12" s="48" t="inlineStr">
+      <c r="B12" s="66" t="inlineStr">
         <is>
           <t>Intel</t>
         </is>
       </c>
-      <c r="C12" s="49" t="inlineStr">
+      <c r="C12" s="67" t="inlineStr">
         <is>
           <t>NASDAQ:INTC</t>
         </is>
@@ -2641,17 +2695,17 @@
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="44" t="inlineStr">
+      <c r="A13" s="62" t="inlineStr">
         <is>
           <t>IREN</t>
         </is>
       </c>
-      <c r="B13" s="45" t="inlineStr">
+      <c r="B13" s="63" t="inlineStr">
         <is>
           <t>IREN</t>
         </is>
       </c>
-      <c r="C13" s="46" t="inlineStr">
+      <c r="C13" s="64" t="inlineStr">
         <is>
           <t>NASDAQ:IREN</t>
         </is>
@@ -2663,17 +2717,17 @@
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="47" t="inlineStr">
+      <c r="A14" s="65" t="inlineStr">
         <is>
           <t>META</t>
         </is>
       </c>
-      <c r="B14" s="48" t="inlineStr">
+      <c r="B14" s="66" t="inlineStr">
         <is>
           <t>Meta Platforms</t>
         </is>
       </c>
-      <c r="C14" s="49" t="inlineStr">
+      <c r="C14" s="67" t="inlineStr">
         <is>
           <t>NASDAQ:META</t>
         </is>
@@ -2685,17 +2739,17 @@
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="44" t="inlineStr">
+      <c r="A15" s="62" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B15" s="45" t="inlineStr">
+      <c r="B15" s="63" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="C15" s="46" t="inlineStr">
+      <c r="C15" s="64" t="inlineStr">
         <is>
           <t>NASDAQ:MSFT</t>
         </is>
@@ -2707,17 +2761,17 @@
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="47" t="inlineStr">
+      <c r="A16" s="65" t="inlineStr">
         <is>
           <t>MU</t>
         </is>
       </c>
-      <c r="B16" s="48" t="inlineStr">
+      <c r="B16" s="66" t="inlineStr">
         <is>
           <t>Micron</t>
         </is>
       </c>
-      <c r="C16" s="49" t="inlineStr">
+      <c r="C16" s="67" t="inlineStr">
         <is>
           <t>NASDAQ:MU</t>
         </is>
@@ -2729,17 +2783,17 @@
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="44" t="inlineStr">
+      <c r="A17" s="62" t="inlineStr">
         <is>
           <t>NFLX</t>
         </is>
       </c>
-      <c r="B17" s="45" t="inlineStr">
+      <c r="B17" s="63" t="inlineStr">
         <is>
           <t>Netflix</t>
         </is>
       </c>
-      <c r="C17" s="46" t="inlineStr">
+      <c r="C17" s="64" t="inlineStr">
         <is>
           <t>NASDAQ:NFLX</t>
         </is>
@@ -2751,17 +2805,17 @@
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="47" t="inlineStr">
+      <c r="A18" s="65" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B18" s="48" t="inlineStr">
+      <c r="B18" s="66" t="inlineStr">
         <is>
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="C18" s="49" t="inlineStr">
+      <c r="C18" s="67" t="inlineStr">
         <is>
           <t>NASDAQ:NVDA</t>
         </is>
@@ -2773,17 +2827,17 @@
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="44" t="inlineStr">
+      <c r="A19" s="62" t="inlineStr">
         <is>
           <t>ORCL</t>
         </is>
       </c>
-      <c r="B19" s="45" t="inlineStr">
+      <c r="B19" s="63" t="inlineStr">
         <is>
           <t>Oracle</t>
         </is>
       </c>
-      <c r="C19" s="46" t="inlineStr">
+      <c r="C19" s="64" t="inlineStr">
         <is>
           <t>NYSE:ORCL</t>
         </is>
@@ -2795,17 +2849,17 @@
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="47" t="inlineStr">
+      <c r="A20" s="65" t="inlineStr">
         <is>
           <t>PFE</t>
         </is>
       </c>
-      <c r="B20" s="48" t="inlineStr">
+      <c r="B20" s="66" t="inlineStr">
         <is>
           <t>Pfizer</t>
         </is>
       </c>
-      <c r="C20" s="49" t="inlineStr">
+      <c r="C20" s="67" t="inlineStr">
         <is>
           <t>NYSE:PFE</t>
         </is>
@@ -2817,17 +2871,17 @@
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="44" t="inlineStr">
+      <c r="A21" s="62" t="inlineStr">
         <is>
           <t>PLTR</t>
         </is>
       </c>
-      <c r="B21" s="45" t="inlineStr">
+      <c r="B21" s="63" t="inlineStr">
         <is>
           <t>Palantir</t>
         </is>
       </c>
-      <c r="C21" s="46" t="inlineStr">
+      <c r="C21" s="64" t="inlineStr">
         <is>
           <t>NASDAQ:PLTR</t>
         </is>
@@ -2839,17 +2893,17 @@
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="47" t="inlineStr">
+      <c r="A22" s="65" t="inlineStr">
         <is>
           <t>QCOM</t>
         </is>
       </c>
-      <c r="B22" s="48" t="inlineStr">
+      <c r="B22" s="66" t="inlineStr">
         <is>
           <t>Qualcomm</t>
         </is>
       </c>
-      <c r="C22" s="49" t="inlineStr">
+      <c r="C22" s="67" t="inlineStr">
         <is>
           <t>NASDAQ:QCOM</t>
         </is>
@@ -2861,17 +2915,17 @@
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="44" t="inlineStr">
+      <c r="A23" s="62" t="inlineStr">
         <is>
           <t>SOFI</t>
         </is>
       </c>
-      <c r="B23" s="45" t="inlineStr">
+      <c r="B23" s="63" t="inlineStr">
         <is>
           <t>SoFi Technologies</t>
         </is>
       </c>
-      <c r="C23" s="46" t="inlineStr">
+      <c r="C23" s="64" t="inlineStr">
         <is>
           <t>NASDAQ:SOFI</t>
         </is>
@@ -2883,17 +2937,17 @@
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="47" t="inlineStr">
+      <c r="A24" s="65" t="inlineStr">
         <is>
           <t>SOXX</t>
         </is>
       </c>
-      <c r="B24" s="48" t="inlineStr">
+      <c r="B24" s="66" t="inlineStr">
         <is>
           <t>iShares 半導體 ETF</t>
         </is>
       </c>
-      <c r="C24" s="49" t="inlineStr">
+      <c r="C24" s="67" t="inlineStr">
         <is>
           <t>NASDAQ:SOXX</t>
         </is>
@@ -2905,17 +2959,17 @@
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="44" t="inlineStr">
+      <c r="A25" s="62" t="inlineStr">
         <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B25" s="45" t="inlineStr">
+      <c r="B25" s="63" t="inlineStr">
         <is>
           <t>Tesla</t>
         </is>
       </c>
-      <c r="C25" s="46" t="inlineStr">
+      <c r="C25" s="64" t="inlineStr">
         <is>
           <t>NASDAQ:TSLA</t>
         </is>
